--- a/backend/data/uploads/PQC/2026-07_공정불량.xlsx
+++ b/backend/data/uploads/PQC/2026-07_공정불량.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\PQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BB24593-BA95-4F52-9141-B45EBA3F5668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F234F99-AB23-459A-9678-57407A57A123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{82FA3E0A-B862-4BCC-B8C9-A63BA16E16D3}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3510F546-4B5E-4A16-B1C8-442FC62BEE14}"/>
   </bookViews>
   <sheets>
     <sheet name="공정불량" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7C1BDA-D78C-4F8D-8804-E259553D0D3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E15F6D2-04C7-43F1-9924-F717618BEA9D}">
   <dimension ref="B2:S9"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/PQC/2026-07_공정불량.xlsx
+++ b/backend/data/uploads/PQC/2026-07_공정불량.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\PQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F234F99-AB23-459A-9678-57407A57A123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E20B5E2E-7CDA-461C-B047-CC6EEB2E65D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3510F546-4B5E-4A16-B1C8-442FC62BEE14}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{63BD6726-F985-4821-9F50-992A8B0E2B12}"/>
   </bookViews>
   <sheets>
     <sheet name="공정불량" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E15F6D2-04C7-43F1-9924-F717618BEA9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A5D3BD-F344-4D50-96E4-7B9570A37D57}">
   <dimension ref="B2:S9"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/PQC/2026-07_공정불량.xlsx
+++ b/backend/data/uploads/PQC/2026-07_공정불량.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\PQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E20B5E2E-7CDA-461C-B047-CC6EEB2E65D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D63B783A-6F7F-451E-A137-1A3D1A3707DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{63BD6726-F985-4821-9F50-992A8B0E2B12}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{8CC0D424-1738-4098-ADD4-A12EB863B4BF}"/>
   </bookViews>
   <sheets>
     <sheet name="공정불량" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A5D3BD-F344-4D50-96E4-7B9570A37D57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F7D5CD-F4BB-4151-A09E-832901F73A0C}">
   <dimension ref="B2:S9"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/PQC/2026-07_공정불량.xlsx
+++ b/backend/data/uploads/PQC/2026-07_공정불량.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\PQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D63B783A-6F7F-451E-A137-1A3D1A3707DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F2A62C-AD2A-4BAE-AA86-4358C688C65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{8CC0D424-1738-4098-ADD4-A12EB863B4BF}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{F3AA6584-3815-415F-93D5-86E17EDDD9E8}"/>
   </bookViews>
   <sheets>
     <sheet name="공정불량" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F7D5CD-F4BB-4151-A09E-832901F73A0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CBBC780-7E68-414B-9FF8-5398E47F553C}">
   <dimension ref="B2:S9"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
